--- a/Adinath Jinalya Best Wishes Sheet.xlsx
+++ b/Adinath Jinalya Best Wishes Sheet.xlsx
@@ -1,36 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jains\IdeaProjects\Adinath-Jinalya-Best-Wishes-Email\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D9B2472-1FE4-4829-83D6-33F6538891E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="26">
-  <si>
-    <t>Recipient Name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="77">
   <si>
     <t>Email</t>
   </si>
   <si>
-    <t>Due Date</t>
-  </si>
-  <si>
     <t>Subject</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>time-zone</t>
-  </si>
-  <si>
     <t>TO LEAD</t>
   </si>
   <si>
@@ -89,50 +89,243 @@
   </si>
   <si>
     <t>sjain-20260815</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>IsKid(Y for Kid, N or blank for Adult)</t>
+  </si>
+  <si>
+    <t>ChildName</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>TimeZone</t>
+  </si>
+  <si>
+    <t>MEHUL DOSHI</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>SEPT 10TH</t>
+  </si>
+  <si>
+    <t>MEHUL'S BIRTHDAY</t>
+  </si>
+  <si>
+    <t>JATIN PATODIA</t>
+  </si>
+  <si>
+    <t>CST</t>
+  </si>
+  <si>
+    <t>JATIN'S BIRTHDAY</t>
+  </si>
+  <si>
+    <t>BOBBY-SONAL JINDAL , SWEET KAVVIESH</t>
+  </si>
+  <si>
+    <t>KAVVIESH</t>
+  </si>
+  <si>
+    <t>SEPT 12TH</t>
+  </si>
+  <si>
+    <t>KAVVIESH'S DAUGHTER BIRTHDAY</t>
+  </si>
+  <si>
+    <t>CHINMAY , PRACHI JAIN AND SWEET NIVEN</t>
+  </si>
+  <si>
+    <t>NIVEN</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>NIVEN ARJIT SON'S BIRTHDAY</t>
+  </si>
+  <si>
+    <t>CHANCHAL , SWATI KALA AND KIAAN</t>
+  </si>
+  <si>
+    <t>KIAAN</t>
+  </si>
+  <si>
+    <t>SEPT 16TH</t>
+  </si>
+  <si>
+    <t>KIAAN'S BIRTHDAY ( SON )</t>
+  </si>
+  <si>
+    <t>RONAK JAIN</t>
+  </si>
+  <si>
+    <t>RONAK'S BIRTHDAY</t>
+  </si>
+  <si>
+    <t>ARVIND AND PRAVEENA BOBRA , SWEET NIRVAAN</t>
+  </si>
+  <si>
+    <t>MST</t>
+  </si>
+  <si>
+    <t>NIRVAAN</t>
+  </si>
+  <si>
+    <t>SEPT 17TH</t>
+  </si>
+  <si>
+    <t>NIRVAAN'S BIRTHDAY</t>
+  </si>
+  <si>
+    <t>JYOTSNA JAIN</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>SEPT 18TH</t>
+  </si>
+  <si>
+    <t>JYOTSNA'S BIRTHDAY</t>
+  </si>
+  <si>
+    <t>ALOK JAIN</t>
+  </si>
+  <si>
+    <t>ALOK'S BIRTHDAY</t>
+  </si>
+  <si>
+    <t>PANKA SHAH</t>
+  </si>
+  <si>
+    <t>PANKAJ'S BIRTHDAY</t>
+  </si>
+  <si>
+    <t>NAINEE GANGWAL</t>
+  </si>
+  <si>
+    <t>NAINEE'S BIRTHDAY</t>
+  </si>
+  <si>
+    <t>YASABH AND NANDINI , SWEET AADIRAJ</t>
+  </si>
+  <si>
+    <t>AADIRAJ</t>
+  </si>
+  <si>
+    <t>AADIRAJ SON'S BIRTHDAY</t>
+  </si>
+  <si>
+    <t>YASH JHAVERI</t>
+  </si>
+  <si>
+    <t>SEPT 19TH</t>
+  </si>
+  <si>
+    <t>YASH'S BIRTHDAY</t>
+  </si>
+  <si>
+    <t>SURESH AJMERA</t>
+  </si>
+  <si>
+    <t>SEPT 1ST</t>
+  </si>
+  <si>
+    <t>SURESH AJMERA'S BIRTHDAY</t>
+  </si>
+  <si>
+    <t>PARAS AND SHRINI PANDYA , SWEET MIHIR</t>
+  </si>
+  <si>
+    <t>MIHIR</t>
+  </si>
+  <si>
+    <t>BIRTHDAY MIHIR DOSHI PANDYA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="10">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="&quot;Google Sans&quot;"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Google Sans Text"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Google Sans Text"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -140,9 +333,27 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F5F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
-    <border/>
+  <borders count="8">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FFC4C7C5"/>
@@ -156,60 +367,165 @@
       <bottom style="thin">
         <color rgb="FFC4C7C5"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -399,289 +715,806 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z29"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="24.75"/>
-    <col customWidth="1" min="2" max="2" width="19.0"/>
-    <col customWidth="1" min="3" max="3" width="15.75"/>
-    <col customWidth="1" min="4" max="4" width="57.0"/>
+    <col min="1" max="1" width="24.77734375" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" customWidth="1"/>
+    <col min="4" max="4" width="57" customWidth="1"/>
+    <col min="8" max="8" width="30.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3">
+        <v>30533</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3">
-        <v>30533.0</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3">
+        <v>30534</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="3">
-        <v>30534.0</v>
-      </c>
-      <c r="D3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:26">
+      <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="B4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="6">
+        <v>30534</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="F4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
+    </row>
+    <row r="5" spans="1:26">
+      <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="s">
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3">
+        <v>30535</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="7">
-        <v>30534.0</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="8" t="s">
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3">
+        <v>30536</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26">
+      <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3">
+        <v>30537</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
-      <c r="X4" s="9"/>
-      <c r="Y4" s="9"/>
-      <c r="Z4" s="9"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="G7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26">
+      <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="3">
-        <v>30535.0</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>30538</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="G8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26">
+      <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="3">
-        <v>30536.0</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3">
+        <v>30539</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3">
+        <v>30540</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26">
+      <c r="A11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="3">
+        <v>30541</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26">
+      <c r="A12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3">
+        <v>30542</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26">
+      <c r="A13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3">
+        <v>30543</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="15.75" customHeight="1" thickBot="1"/>
+    <row r="15" spans="1:26" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A15" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="10">
+        <v>46246</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="12"/>
+      <c r="F15" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" s="13"/>
+    </row>
+    <row r="16" spans="1:26" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A16" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="15">
+        <v>46246</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="17"/>
+      <c r="F16" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="M16" s="13"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A17" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="15">
+        <v>46246</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="17"/>
+      <c r="F17" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="J17" s="17"/>
+      <c r="K17" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="M17" s="13"/>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A18" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="15">
+        <v>46246</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="17"/>
+      <c r="F18" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="3">
-        <v>30537.0</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="3">
-        <v>30538.0</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="3">
-        <v>30539.0</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="G18" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M18" s="13"/>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A19" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="15">
+        <v>46247</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="17"/>
+      <c r="F19" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="M19" s="13"/>
+    </row>
+    <row r="20" spans="1:13" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A20" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="15">
+        <v>46247</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="17"/>
+      <c r="F20" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M20" s="13"/>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A21" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="15">
+        <v>46247</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="17"/>
+      <c r="F21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="J21" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M21" s="13"/>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A22" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="15">
+        <v>46247</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="17"/>
+      <c r="F22" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M22" s="13"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A23" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="15">
+        <v>46248</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="17"/>
+      <c r="F23" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M23" s="13"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A24" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="15">
+        <v>46248</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="17"/>
+      <c r="F24" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M24" s="13"/>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A25" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="15">
+        <v>46248</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="17"/>
+      <c r="F25" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M25" s="13"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A26" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="15">
+        <v>46248</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="17"/>
+      <c r="F26" s="16" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="3">
-        <v>30540.0</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="1" t="s">
+      <c r="G26" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J26" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M26" s="13"/>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A27" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="15">
+        <v>46248</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="17"/>
+      <c r="F27" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M27" s="13"/>
+    </row>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A28" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="15">
+        <v>46248</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="17"/>
+      <c r="F28" s="16" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="3">
-        <v>30541.0</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="3">
-        <v>30542.0</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="3">
-        <v>30543.0</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="G28" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M28" s="13"/>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A29" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="15">
+        <v>46248</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="17"/>
+      <c r="F29" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="J29" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M29" s="13"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>